--- a/datasets/llama_ready_for_human_scoring.xlsx
+++ b/datasets/llama_ready_for_human_scoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yusun's computer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7FB85C-50D7-45E5-9E9B-6DE088A47D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576B5D7A-2E9A-488D-AD84-ACFE75DEF680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
